--- a/data/trans_dic/P16A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,25</t>
+          <t>2,18; 7,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 13,81</t>
+          <t>6,9; 14,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,64</t>
+          <t>4,93; 11,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 9,67</t>
+          <t>4,39; 9,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 16,01</t>
+          <t>8,14; 16,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,27; 24,25</t>
+          <t>14,36; 24,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,05; 23,4</t>
+          <t>13,69; 23,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,87; 15,45</t>
+          <t>9,97; 15,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,39</t>
+          <t>5,82; 10,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,76; 17,75</t>
+          <t>11,7; 17,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,32; 16,07</t>
+          <t>10,18; 15,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 11,62</t>
+          <t>7,7; 11,58</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,57</t>
+          <t>2,25; 5,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 9,0</t>
+          <t>3,82; 8,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,02</t>
+          <t>3,78; 8,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 11,04</t>
+          <t>5,72; 10,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,1; 16,09</t>
+          <t>9,9; 15,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,58; 20,57</t>
+          <t>13,6; 20,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 18,06</t>
+          <t>11,3; 17,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,49; 19,81</t>
+          <t>14,64; 20,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 10,29</t>
+          <t>6,76; 10,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 13,46</t>
+          <t>9,42; 13,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 12,22</t>
+          <t>8,37; 12,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,71</t>
+          <t>10,76; 14,55</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,52</t>
+          <t>1,46; 5,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 12,21</t>
+          <t>5,48; 12,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,23</t>
+          <t>1,93; 6,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 13,42</t>
+          <t>7,48; 13,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 8,24</t>
+          <t>3,3; 8,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,95; 17,26</t>
+          <t>9,97; 17,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,85; 15,93</t>
+          <t>8,83; 15,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,27; 22,02</t>
+          <t>15,47; 22,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,19</t>
+          <t>2,87; 5,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,48</t>
+          <t>8,59; 13,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 10,32</t>
+          <t>6,16; 10,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,43; 16,94</t>
+          <t>12,29; 17,04</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,4</t>
+          <t>1,35; 4,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,01</t>
+          <t>2,93; 7,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,63</t>
+          <t>3,74; 8,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 13,03</t>
+          <t>5,9; 12,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 11,67</t>
+          <t>6,27; 12,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,6; 21,1</t>
+          <t>13,85; 21,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,4; 20,01</t>
+          <t>12,55; 20,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 14,24</t>
+          <t>6,21; 14,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,74</t>
+          <t>4,35; 7,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 13,8</t>
+          <t>9,07; 13,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 13,72</t>
+          <t>8,93; 13,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 12,75</t>
+          <t>6,98; 12,28</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,93</t>
+          <t>3,94; 10,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 8,86</t>
+          <t>2,59; 9,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 14,18</t>
+          <t>6,16; 14,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 9,58</t>
+          <t>4,2; 9,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 21,66</t>
+          <t>11,22; 21,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,47; 32,59</t>
+          <t>20,44; 32,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,98; 22,5</t>
+          <t>11,97; 22,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,08; 18,2</t>
+          <t>7,58; 18,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 14,66</t>
+          <t>8,68; 14,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,58; 19,69</t>
+          <t>12,16; 19,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 16,58</t>
+          <t>10,01; 16,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 13,28</t>
+          <t>7,63; 13,33</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,7</t>
+          <t>0,74; 4,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,7; 11,64</t>
+          <t>4,68; 11,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,89; 9,97</t>
+          <t>4,03; 10,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,6; 14,65</t>
+          <t>8,49; 14,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,42</t>
+          <t>4,26; 10,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,23; 19,91</t>
+          <t>11,72; 20,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,04; 22,23</t>
+          <t>13,39; 22,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,27; 26,67</t>
+          <t>19,23; 26,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,51</t>
+          <t>2,89; 6,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,98; 14,36</t>
+          <t>8,98; 14,59</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,64; 15,26</t>
+          <t>9,6; 15,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,56; 19,44</t>
+          <t>14,4; 19,44</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,91</t>
+          <t>3,28; 6,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,05</t>
+          <t>5,1; 9,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,66</t>
+          <t>5,51; 9,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 11,51</t>
+          <t>6,51; 11,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,34; 14,26</t>
+          <t>9,54; 14,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,45; 14,49</t>
+          <t>9,5; 14,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,03; 16,84</t>
+          <t>11,45; 17,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,95; 19,28</t>
+          <t>6,73; 19,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,0; 10,0</t>
+          <t>6,85; 10,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,15</t>
+          <t>7,89; 11,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,2; 12,7</t>
+          <t>9,02; 12,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,46; 14,3</t>
+          <t>7,42; 14,48</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,71; 10,82</t>
+          <t>6,56; 10,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,06</t>
+          <t>4,52; 8,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,08</t>
+          <t>3,91; 7,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,25</t>
+          <t>3,11; 10,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,88; 15,79</t>
+          <t>10,84; 15,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,9; 16,99</t>
+          <t>12,02; 17,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,77; 18,09</t>
+          <t>13,02; 18,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,94; 23,22</t>
+          <t>18,2; 23,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,36; 12,61</t>
+          <t>9,24; 12,65</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,92; 11,95</t>
+          <t>8,84; 12,04</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,92; 12,19</t>
+          <t>9,01; 12,37</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,28; 15,82</t>
+          <t>7,31; 15,87</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,75</t>
+          <t>4,2; 5,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,62</t>
+          <t>5,79; 7,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,16</t>
+          <t>5,44; 7,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,53; 9,39</t>
+          <t>6,43; 9,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,1; 12,25</t>
+          <t>10,06; 12,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,42; 16,8</t>
+          <t>14,27; 16,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,98; 16,45</t>
+          <t>13,94; 16,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,89; 17,68</t>
+          <t>13,22; 17,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,45; 8,85</t>
+          <t>7,51; 8,75</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10,43; 12,04</t>
+          <t>10,48; 12,04</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,04; 11,57</t>
+          <t>10,08; 11,54</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,81; 13,44</t>
+          <t>10,6; 13,41</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6010; 19784</t>
+          <t>5938; 20369</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18986; 40691</t>
+          <t>20323; 41999</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14489; 34181</t>
+          <t>14495; 33606</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13391; 30128</t>
+          <t>13669; 30646</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21328; 41757</t>
+          <t>21244; 42772</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40999; 69644</t>
+          <t>41240; 69168</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40570; 67561</t>
+          <t>39533; 67262</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28590; 44752</t>
+          <t>28873; 45878</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30383; 55447</t>
+          <t>31087; 56199</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68423; 103296</t>
+          <t>68081; 102496</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60095; 93596</t>
+          <t>59316; 93098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46491; 69816</t>
+          <t>46266; 69623</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10912; 27471</t>
+          <t>11094; 27826</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17846; 45511</t>
+          <t>19336; 45203</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19481; 40324</t>
+          <t>18987; 40522</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29577; 57227</t>
+          <t>29635; 56399</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50888; 81064</t>
+          <t>49890; 80043</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71151; 107753</t>
+          <t>71242; 107494</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61286; 94490</t>
+          <t>59083; 91712</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74630; 102030</t>
+          <t>75397; 102971</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67010; 102606</t>
+          <t>67436; 99728</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95984; 138512</t>
+          <t>97000; 140466</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86160; 125323</t>
+          <t>85801; 126764</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>111738; 151973</t>
+          <t>111149; 150351</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4302; 17586</t>
+          <t>4663; 17579</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17173; 39551</t>
+          <t>17771; 39303</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6099; 19840</t>
+          <t>6133; 21004</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23256; 42399</t>
+          <t>23641; 42925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11039; 27654</t>
+          <t>11056; 27513</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33935; 58873</t>
+          <t>34005; 60105</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29747; 53589</t>
+          <t>29698; 53239</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53329; 76879</t>
+          <t>54022; 76949</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18995; 40520</t>
+          <t>18748; 38882</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56306; 89642</t>
+          <t>57114; 89416</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39940; 67598</t>
+          <t>40369; 68049</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82678; 112698</t>
+          <t>81784; 113359</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5504; 19382</t>
+          <t>4836; 17298</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11618; 29958</t>
+          <t>10975; 27948</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14448; 31942</t>
+          <t>13843; 32767</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18318; 40739</t>
+          <t>18433; 39487</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22746; 43352</t>
+          <t>23302; 45018</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52891; 82052</t>
+          <t>53864; 83057</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48041; 77484</t>
+          <t>48588; 78621</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29417; 67742</t>
+          <t>29534; 66937</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32506; 56541</t>
+          <t>31748; 56000</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70450; 105288</t>
+          <t>69212; 105313</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>66675; 103881</t>
+          <t>67592; 101648</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57908; 100520</t>
+          <t>55018; 96786</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7997; 22213</t>
+          <t>8017; 21502</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5410; 18831</t>
+          <t>5502; 19663</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13052; 29957</t>
+          <t>13004; 29994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7615; 17115</t>
+          <t>7507; 17355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23817; 44973</t>
+          <t>23292; 45132</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44942; 71564</t>
+          <t>44886; 71758</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26188; 49190</t>
+          <t>26168; 49097</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18330; 47095</t>
+          <t>19620; 47409</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35073; 60249</t>
+          <t>35677; 61197</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54372; 85081</t>
+          <t>52560; 84363</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44438; 71273</t>
+          <t>43037; 70618</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32349; 58086</t>
+          <t>33388; 58300</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2808; 12725</t>
+          <t>2000; 11792</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12871; 31889</t>
+          <t>12831; 31593</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10231; 26221</t>
+          <t>10616; 27076</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23179; 39498</t>
+          <t>22880; 39072</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11979; 28978</t>
+          <t>11837; 29082</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31454; 55749</t>
+          <t>32813; 57550</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35628; 60708</t>
+          <t>36559; 61747</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49523; 68569</t>
+          <t>49444; 68945</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16385; 35719</t>
+          <t>15886; 35404</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49748; 79575</t>
+          <t>49776; 80827</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51702; 81841</t>
+          <t>51483; 82665</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>76674; 102392</t>
+          <t>75853; 102368</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19516; 42529</t>
+          <t>20170; 40657</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33234; 60013</t>
+          <t>33814; 62140</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35099; 63449</t>
+          <t>36199; 64245</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41122; 71854</t>
+          <t>40648; 69825</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>59606; 91026</t>
+          <t>60878; 92381</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65583; 100562</t>
+          <t>65925; 100695</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>76280; 116415</t>
+          <t>79159; 118235</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>58991; 163737</t>
+          <t>57128; 165307</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>87690; 125359</t>
+          <t>85841; 126190</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>106633; 151306</t>
+          <t>107036; 153799</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>123990; 171187</t>
+          <t>121602; 168037</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>109878; 210708</t>
+          <t>109384; 213349</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>49937; 80482</t>
+          <t>48761; 79469</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>34899; 62782</t>
+          <t>35239; 63769</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30058; 55118</t>
+          <t>30433; 55973</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25771; 95191</t>
+          <t>28858; 95023</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>85261; 123694</t>
+          <t>84933; 122439</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>98045; 140011</t>
+          <t>99000; 141810</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>105501; 149433</t>
+          <t>107558; 151988</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>128753; 166664</t>
+          <t>130597; 168755</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>142900; 192593</t>
+          <t>141071; 193243</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>142972; 191586</t>
+          <t>141752; 192952</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>143099; 195555</t>
+          <t>144601; 198505</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>136298; 260511</t>
+          <t>120395; 261356</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>137978; 188322</t>
+          <t>137711; 186644</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>198997; 261076</t>
+          <t>198349; 262165</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>187163; 243107</t>
+          <t>184534; 240749</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>225782; 324905</t>
+          <t>222400; 320799</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>341295; 413853</t>
+          <t>339971; 408540</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>513093; 597912</t>
+          <t>507726; 595880</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>495516; 583035</t>
+          <t>494082; 583729</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>478497; 656282</t>
+          <t>490632; 660644</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>495709; 588787</t>
+          <t>499543; 582131</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>728374; 840686</t>
+          <t>732170; 840872</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>696759; 802928</t>
+          <t>699388; 800588</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>775592; 964118</t>
+          <t>760517; 961645</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,46</t>
+          <t>2,07; 7,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 14,25</t>
+          <t>6,51; 14,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,44</t>
+          <t>4,93; 11,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,84</t>
+          <t>4,52; 9,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 16,4</t>
+          <t>7,99; 15,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,36; 24,08</t>
+          <t>14,63; 24,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,69; 23,3</t>
+          <t>13,88; 23,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,97; 15,84</t>
+          <t>9,41; 14,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,53</t>
+          <t>5,93; 10,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,7; 17,61</t>
+          <t>11,58; 17,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 15,98</t>
+          <t>10,16; 16,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,58</t>
+          <t>7,62; 11,25</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,64</t>
+          <t>2,34; 5,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,94</t>
+          <t>3,62; 8,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,06</t>
+          <t>4,1; 8,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 10,88</t>
+          <t>5,61; 11,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,9; 15,88</t>
+          <t>10,01; 15,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,6; 20,52</t>
+          <t>13,83; 20,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 17,53</t>
+          <t>11,5; 18,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,64; 20,0</t>
+          <t>14,32; 19,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,0</t>
+          <t>6,71; 10,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,42; 13,65</t>
+          <t>9,45; 13,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,37; 12,36</t>
+          <t>8,37; 12,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 14,55</t>
+          <t>10,91; 14,64</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,51</t>
+          <t>1,51; 5,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,13</t>
+          <t>5,46; 12,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,59</t>
+          <t>1,99; 6,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 13,58</t>
+          <t>7,41; 13,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 8,2</t>
+          <t>3,28; 8,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,97; 17,63</t>
+          <t>9,74; 17,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,83; 15,83</t>
+          <t>8,84; 15,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,47; 22,04</t>
+          <t>15,57; 21,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,94</t>
+          <t>2,88; 6,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,59; 13,44</t>
+          <t>8,68; 13,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,39</t>
+          <t>6,0; 10,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,29; 17,04</t>
+          <t>12,44; 16,87</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,82</t>
+          <t>1,38; 4,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,47</t>
+          <t>3,13; 7,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 8,86</t>
+          <t>3,74; 8,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 12,63</t>
+          <t>5,32; 11,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 12,12</t>
+          <t>6,35; 12,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,85; 21,35</t>
+          <t>13,36; 20,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,55; 20,3</t>
+          <t>12,56; 20,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 14,07</t>
+          <t>10,32; 16,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 7,67</t>
+          <t>4,34; 7,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,07; 13,8</t>
+          <t>9,03; 13,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,93; 13,42</t>
+          <t>8,98; 13,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 12,28</t>
+          <t>8,71; 13,0</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 10,58</t>
+          <t>4,06; 10,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 9,25</t>
+          <t>2,71; 9,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 14,2</t>
+          <t>5,53; 13,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 9,71</t>
+          <t>3,63; 8,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,22; 21,73</t>
+          <t>12,13; 22,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,44; 32,68</t>
+          <t>20,38; 32,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,97; 22,46</t>
+          <t>12,32; 22,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 18,32</t>
+          <t>13,82; 20,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,68; 14,89</t>
+          <t>8,54; 14,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,16; 19,52</t>
+          <t>12,15; 19,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,43</t>
+          <t>10,06; 16,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 13,33</t>
+          <t>9,56; 13,79</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,35</t>
+          <t>0,73; 4,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,68; 11,53</t>
+          <t>4,63; 11,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,29</t>
+          <t>4,04; 10,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,49; 14,49</t>
+          <t>8,53; 14,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,46</t>
+          <t>4,31; 10,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,72; 20,55</t>
+          <t>11,42; 19,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,39; 22,61</t>
+          <t>12,88; 21,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,23; 26,82</t>
+          <t>19,03; 26,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,45</t>
+          <t>3,06; 6,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,98; 14,59</t>
+          <t>9,14; 14,29</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,6; 15,42</t>
+          <t>9,38; 15,08</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,4; 19,44</t>
+          <t>14,57; 19,16</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,61</t>
+          <t>3,24; 6,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,38</t>
+          <t>5,0; 9,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,51; 9,79</t>
+          <t>5,35; 9,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,18</t>
+          <t>6,58; 11,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,54; 14,47</t>
+          <t>9,25; 14,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,5; 14,51</t>
+          <t>9,62; 14,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,45; 17,1</t>
+          <t>11,56; 17,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 19,46</t>
+          <t>15,85; 20,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,85; 10,07</t>
+          <t>7,02; 10,04</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,89; 11,34</t>
+          <t>7,72; 10,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,02; 12,47</t>
+          <t>9,02; 12,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,42; 14,48</t>
+          <t>11,96; 15,36</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,68</t>
+          <t>6,53; 10,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,18</t>
+          <t>4,34; 7,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,19</t>
+          <t>3,86; 7,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,23</t>
+          <t>7,6; 11,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,84; 15,63</t>
+          <t>10,79; 15,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,02; 17,21</t>
+          <t>11,96; 16,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,02; 18,4</t>
+          <t>13,02; 18,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,2; 23,51</t>
+          <t>17,43; 22,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,24; 12,65</t>
+          <t>9,38; 12,6</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,84; 12,04</t>
+          <t>8,93; 12,03</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,01; 12,37</t>
+          <t>8,97; 12,36</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,31; 15,87</t>
+          <t>13,24; 16,29</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,7</t>
+          <t>4,14; 5,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,65</t>
+          <t>5,7; 7,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,09</t>
+          <t>5,51; 7,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,27</t>
+          <t>7,67; 9,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,06; 12,09</t>
+          <t>10,14; 12,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,27; 16,75</t>
+          <t>14,5; 16,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,94; 16,47</t>
+          <t>14,11; 16,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,22; 17,8</t>
+          <t>16,41; 18,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,75</t>
+          <t>7,44; 8,81</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10,48; 12,04</t>
+          <t>10,42; 11,95</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,08; 11,54</t>
+          <t>10,04; 11,57</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,6; 13,41</t>
+          <t>12,46; 13,88</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>21304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36320</t>
+          <t>37471</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56984</t>
+          <t>58775</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5938; 20369</t>
+          <t>5640; 19443</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20323; 41999</t>
+          <t>19177; 41495</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14495; 33606</t>
+          <t>14489; 33356</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13669; 30646</t>
+          <t>14397; 31708</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21244; 42772</t>
+          <t>20838; 41535</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41240; 69168</t>
+          <t>42036; 69661</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39533; 67262</t>
+          <t>40071; 67407</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28873; 45878</t>
+          <t>29733; 46206</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31087; 56199</t>
+          <t>31677; 58633</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68081; 102496</t>
+          <t>67380; 102720</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59316; 93098</t>
+          <t>59188; 93736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46266; 69623</t>
+          <t>48392; 71416</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41872</t>
+          <t>43751</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87965</t>
+          <t>91496</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>129838</t>
+          <t>135247</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11094; 27826</t>
+          <t>11547; 29141</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19336; 45203</t>
+          <t>18312; 44335</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18987; 40522</t>
+          <t>20616; 40659</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29635; 56399</t>
+          <t>29785; 60263</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49890; 80043</t>
+          <t>50436; 79435</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71242; 107494</t>
+          <t>72432; 107204</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59083; 91712</t>
+          <t>60144; 94352</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75397; 102971</t>
+          <t>78234; 106541</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67436; 99728</t>
+          <t>66929; 101034</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97000; 140466</t>
+          <t>97220; 142729</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>85801; 126764</t>
+          <t>85864; 126099</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>111149; 150351</t>
+          <t>117489; 157644</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>32113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64931</t>
+          <t>66347</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96187</t>
+          <t>98459</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4663; 17579</t>
+          <t>4827; 18327</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17771; 39303</t>
+          <t>17692; 40156</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6133; 21004</t>
+          <t>6341; 20577</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23641; 42925</t>
+          <t>23416; 42850</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11056; 27513</t>
+          <t>10987; 27724</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34005; 60105</t>
+          <t>33208; 58996</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29698; 53239</t>
+          <t>29745; 52604</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54022; 76949</t>
+          <t>55480; 78229</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18748; 38882</t>
+          <t>18848; 39532</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57114; 89416</t>
+          <t>57741; 90377</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40369; 68049</t>
+          <t>39303; 67436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81784; 113359</t>
+          <t>83676; 113410</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>29717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>50013</t>
+          <t>54666</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77554</t>
+          <t>84383</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4836; 17298</t>
+          <t>4957; 17784</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10975; 27948</t>
+          <t>11693; 29377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13843; 32767</t>
+          <t>13854; 31669</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18433; 39487</t>
+          <t>19869; 44514</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23302; 45018</t>
+          <t>23603; 45231</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53864; 83057</t>
+          <t>51967; 81327</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48588; 78621</t>
+          <t>48636; 78416</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29534; 66937</t>
+          <t>43552; 68502</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31748; 56000</t>
+          <t>31702; 57461</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69212; 105313</t>
+          <t>68902; 104034</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67592; 101648</t>
+          <t>68024; 104754</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>55018; 96786</t>
+          <t>69232; 103333</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36150</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47735</t>
+          <t>50289</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8017; 21502</t>
+          <t>8261; 22037</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5502; 19663</t>
+          <t>5755; 20225</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13004; 29994</t>
+          <t>11683; 29428</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7507; 17355</t>
+          <t>7462; 17851</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23292; 45132</t>
+          <t>25182; 47292</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44886; 71758</t>
+          <t>44749; 71665</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26168; 49097</t>
+          <t>26926; 48866</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19620; 47409</t>
+          <t>31625; 46095</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35677; 61197</t>
+          <t>35092; 61265</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52560; 84363</t>
+          <t>52504; 83059</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43037; 70618</t>
+          <t>43252; 71996</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33388; 58300</t>
+          <t>41528; 59911</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30397</t>
+          <t>29805</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>58116</t>
+          <t>59303</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88514</t>
+          <t>89108</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2000; 11792</t>
+          <t>1975; 12672</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12831; 31593</t>
+          <t>12684; 30682</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10616; 27076</t>
+          <t>10642; 27485</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22880; 39072</t>
+          <t>23084; 38660</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11837; 29082</t>
+          <t>11986; 28797</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32813; 57550</t>
+          <t>31992; 55890</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36559; 61747</t>
+          <t>35166; 59431</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49444; 68945</t>
+          <t>50185; 69556</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15886; 35404</t>
+          <t>16804; 35574</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49776; 80827</t>
+          <t>50664; 79159</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51483; 82665</t>
+          <t>50322; 80873</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>75853; 102368</t>
+          <t>77884; 102402</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53744</t>
+          <t>62323</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>120446</t>
+          <t>140574</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>174190</t>
+          <t>202897</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20170; 40657</t>
+          <t>19912; 40830</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33814; 62140</t>
+          <t>33136; 62015</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36199; 64245</t>
+          <t>35133; 62970</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40648; 69825</t>
+          <t>47350; 79702</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>60878; 92381</t>
+          <t>59051; 93378</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65925; 100695</t>
+          <t>66725; 101333</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79159; 118235</t>
+          <t>79884; 117989</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>57128; 165307</t>
+          <t>122395; 160922</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>85841; 126190</t>
+          <t>87962; 125881</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>107036; 153799</t>
+          <t>104771; 147369</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>121602; 168037</t>
+          <t>121519; 169823</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>109384; 213349</t>
+          <t>178407; 229186</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>65541</t>
+          <t>74114</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>148102</t>
+          <t>164511</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>213643</t>
+          <t>238625</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>48761; 79469</t>
+          <t>48606; 78340</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>35239; 63769</t>
+          <t>33787; 60860</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30433; 55973</t>
+          <t>30035; 55012</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28858; 95023</t>
+          <t>60693; 91007</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>84933; 122439</t>
+          <t>84535; 124044</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>99000; 141810</t>
+          <t>98548; 138589</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>107558; 151988</t>
+          <t>107554; 154332</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>130597; 168755</t>
+          <t>144867; 186134</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>141071; 193243</t>
+          <t>143314; 192377</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>141752; 192952</t>
+          <t>143109; 192886</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>144601; 198505</t>
+          <t>144001; 198418</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>120395; 261356</t>
+          <t>215795; 265504</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>282602</t>
+          <t>305311</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>602042</t>
+          <t>652472</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>884644</t>
+          <t>957783</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>137711; 186644</t>
+          <t>135663; 187471</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>198349; 262165</t>
+          <t>195270; 259956</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>184534; 240749</t>
+          <t>186862; 243370</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>222400; 320799</t>
+          <t>270968; 339187</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>339971; 408540</t>
+          <t>342761; 412231</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>507726; 595880</t>
+          <t>515873; 602809</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>494082; 583729</t>
+          <t>500061; 586337</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>490632; 660644</t>
+          <t>613414; 689803</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>499543; 582131</t>
+          <t>495382; 586238</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>732170; 840872</t>
+          <t>727951; 834702</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>699388; 800588</t>
+          <t>696469; 802855</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>760517; 961645</t>
+          <t>906063; 1009350</t>
         </is>
       </c>
     </row>
